--- a/assets/ESR Formations-Russia.xlsx
+++ b/assets/ESR Formations-Russia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9EFA18F7C2E81EA4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{E90DCEA3-0D93-4AD5-83F7-85788FB57FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5C2C2C5-C7E6-4FA7-9830-2F290E9B850C}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{E90DCEA3-0D93-4AD5-83F7-85788FB57FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12A74593-D65D-4D6F-9326-2F422DA0DE98}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="510" windowWidth="26610" windowHeight="14700" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="-27840" yWindow="705" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="73">
   <si>
     <t>Formation</t>
   </si>
@@ -181,90 +181,6 @@
     <t>Limit one Rezervnaya Artilleriya per Force</t>
   </si>
   <si>
-    <t>Leib-Gvardii Yegerskiy</t>
-  </si>
-  <si>
-    <t>Leib-Gvardii Pehotniy</t>
-  </si>
-  <si>
-    <t>Kavalergardskiy</t>
-  </si>
-  <si>
-    <t>Leib-Gvardii Konnyy</t>
-  </si>
-  <si>
-    <t>Yego Velichestva Leib-Kirasirskiy</t>
-  </si>
-  <si>
-    <t>Yeya Velichestva Kirasirskiy</t>
-  </si>
-  <si>
-    <t>Leib-Gvardii Dragunskiy</t>
-  </si>
-  <si>
-    <t>Leib-Gvardii Ulanskiy</t>
-  </si>
-  <si>
-    <t>Leib-Gvardii Gusarskiy</t>
-  </si>
-  <si>
-    <t>Leib-Gvardii Kazachiy</t>
-  </si>
-  <si>
-    <t>Yegerskiy</t>
-  </si>
-  <si>
-    <t>Pehotniy</t>
-  </si>
-  <si>
-    <t>Grenaderskaya</t>
-  </si>
-  <si>
-    <t>Svodno-Grenaderskaya</t>
-  </si>
-  <si>
-    <t>Pionery</t>
-  </si>
-  <si>
-    <t>Kirasirskiy</t>
-  </si>
-  <si>
-    <t>Dragunskiy</t>
-  </si>
-  <si>
-    <t>Ulanskiy</t>
-  </si>
-  <si>
-    <t>Gusarskiy</t>
-  </si>
-  <si>
-    <t>Donskoy Kazachiy</t>
-  </si>
-  <si>
-    <t>Konno-Tatarskiy</t>
-  </si>
-  <si>
-    <t>Bugskiy Kazachiy</t>
-  </si>
-  <si>
-    <t>Bashkirskiy Konnyy</t>
-  </si>
-  <si>
-    <t>Teptyar Kazachiy</t>
-  </si>
-  <si>
-    <t>Batareynaya Artilleriyskaya</t>
-  </si>
-  <si>
-    <t>Legkaya Artilleriyskaya</t>
-  </si>
-  <si>
-    <t>Konno-Artilleriyskaya</t>
-  </si>
-  <si>
-    <t>Donskoy Artilleriyskaya</t>
-  </si>
-  <si>
     <t>RU Pehotnaya Diviziya</t>
   </si>
   <si>
@@ -296,6 +212,90 @@
   </si>
   <si>
     <t xml:space="preserve">	Rapid Deployment</t>
+  </si>
+  <si>
+    <t>RU Leib-Gvardii Yegerskiy</t>
+  </si>
+  <si>
+    <t>RU Leib-Gvardii Pehotniy</t>
+  </si>
+  <si>
+    <t>RU Kavalergardskiy</t>
+  </si>
+  <si>
+    <t>RU Leib-Gvardii Konnyy</t>
+  </si>
+  <si>
+    <t>RU Yego Velichestva Leib-Kirasirskiy</t>
+  </si>
+  <si>
+    <t>RU Yeya Velichestva Kirasirskiy</t>
+  </si>
+  <si>
+    <t>RU Leib-Gvardii Dragunskiy</t>
+  </si>
+  <si>
+    <t>RU Leib-Gvardii Ulanskiy</t>
+  </si>
+  <si>
+    <t>RU Leib-Gvardii Gusarskiy</t>
+  </si>
+  <si>
+    <t>RU Leib-Gvardii Kazachiy</t>
+  </si>
+  <si>
+    <t>RU Yegerskiy</t>
+  </si>
+  <si>
+    <t>RU Pehotniy</t>
+  </si>
+  <si>
+    <t>RU Grenaderskaya</t>
+  </si>
+  <si>
+    <t>RU Svodno-Grenaderskaya</t>
+  </si>
+  <si>
+    <t>RU Pionery</t>
+  </si>
+  <si>
+    <t>RU Kirasirskiy</t>
+  </si>
+  <si>
+    <t>RU Dragunskiy</t>
+  </si>
+  <si>
+    <t>RU Ulanskiy</t>
+  </si>
+  <si>
+    <t>RU Gusarskiy</t>
+  </si>
+  <si>
+    <t>RU Donskoy Kazachiy</t>
+  </si>
+  <si>
+    <t>RU Konno-Tatarskiy</t>
+  </si>
+  <si>
+    <t>RU Bugskiy Kazachiy</t>
+  </si>
+  <si>
+    <t>RU Bashkirskiy Konnyy</t>
+  </si>
+  <si>
+    <t>RU Teptyar Kazachiy</t>
+  </si>
+  <si>
+    <t>RU Batareynaya Artilleriyskaya</t>
+  </si>
+  <si>
+    <t>RU Legkaya Artilleriyskaya</t>
+  </si>
+  <si>
+    <t>RU Konno-Artilleriyskaya</t>
+  </si>
+  <si>
+    <t>RU Donskoy Artilleriyskaya</t>
   </si>
 </sst>
 </file>
@@ -434,10 +434,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -810,36 +810,36 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="11"/>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="3">
         <v>4</v>
       </c>
-      <c r="F2" s="12"/>
+      <c r="F2" s="11"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
       <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="3">
         <v>8</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="11"/>
       <c r="I3" s="8" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>13</v>
@@ -847,7 +847,7 @@
     </row>
     <row r="4" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>6</v>
@@ -865,7 +865,7 @@
         <v>23</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>13</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="5" spans="1:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -887,20 +887,20 @@
       </c>
       <c r="F5" s="2"/>
       <c r="I5" s="8" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="A6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -909,27 +909,27 @@
       <c r="E6" s="5">
         <v>8</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="12"/>
       <c r="I6" s="8" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
       <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
       </c>
-      <c r="F7" s="11"/>
+      <c r="F7" s="12"/>
       <c r="I7" s="8" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>15</v>
@@ -937,7 +937,7 @@
     </row>
     <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
@@ -953,7 +953,7 @@
       </c>
       <c r="F8" s="2"/>
       <c r="I8" s="8" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>15</v>
@@ -961,7 +961,7 @@
     </row>
     <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>7</v>
@@ -977,123 +977,123 @@
       </c>
       <c r="F9" s="4"/>
       <c r="I9" s="8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="13">
         <v>6</v>
       </c>
-      <c r="F10" s="12"/>
+      <c r="F10" s="11"/>
       <c r="I10" s="8" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
       <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="12"/>
+      <c r="D11" s="11"/>
       <c r="E11" s="13"/>
-      <c r="F11" s="12"/>
+      <c r="F11" s="11"/>
       <c r="I11" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="10"/>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="5">
         <v>2</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="12"/>
       <c r="I13" s="8" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="5">
         <v>2</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="12"/>
       <c r="I14" s="8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5">
         <v>2</v>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="12"/>
       <c r="I15" s="8" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>13</v>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>6</v>
@@ -1113,7 +1113,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="2"/>
       <c r="I16" s="8" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>13</v>
@@ -1121,16 +1121,16 @@
     </row>
     <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>14</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I18" s="8" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>15</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I19" s="9" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>15</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I20" s="9" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>15</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I21" s="9" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>15</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I22" s="9" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>15</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I23" s="9" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>15</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I24" s="9" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>15</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I25" s="9" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>15</v>
@@ -1202,15 +1202,15 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I26" s="9" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="I27" s="9" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>16</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I28" s="9" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>16</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I29" s="9" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>16</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I30" s="9" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>16</v>
@@ -1242,6 +1242,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -1258,7 +1259,6 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1285,88 +1285,88 @@
       </c>
       <c r="D1" s="9" t="str" cm="1">
         <f t="array" ref="D1:AE1">TRANSPOSE( BaselineFormations!I3:I30 )</f>
-        <v>Leib-Gvardii Yegerskiy</v>
+        <v>RU Leib-Gvardii Yegerskiy</v>
       </c>
       <c r="E1" s="9" t="str">
-        <v>Leib-Gvardii Pehotniy</v>
+        <v>RU Leib-Gvardii Pehotniy</v>
       </c>
       <c r="F1" s="9" t="str">
-        <v>Kavalergardskiy</v>
+        <v>RU Kavalergardskiy</v>
       </c>
       <c r="G1" s="9" t="str">
-        <v>Leib-Gvardii Konnyy</v>
+        <v>RU Leib-Gvardii Konnyy</v>
       </c>
       <c r="H1" s="9" t="str">
-        <v>Yego Velichestva Leib-Kirasirskiy</v>
+        <v>RU Yego Velichestva Leib-Kirasirskiy</v>
       </c>
       <c r="I1" s="9" t="str">
-        <v>Yeya Velichestva Kirasirskiy</v>
+        <v>RU Yeya Velichestva Kirasirskiy</v>
       </c>
       <c r="J1" s="9" t="str">
-        <v>Leib-Gvardii Dragunskiy</v>
+        <v>RU Leib-Gvardii Dragunskiy</v>
       </c>
       <c r="K1" s="9" t="str">
-        <v>Leib-Gvardii Ulanskiy</v>
+        <v>RU Leib-Gvardii Ulanskiy</v>
       </c>
       <c r="L1" s="9" t="str">
-        <v>Leib-Gvardii Gusarskiy</v>
+        <v>RU Leib-Gvardii Gusarskiy</v>
       </c>
       <c r="M1" s="9" t="str">
-        <v>Leib-Gvardii Kazachiy</v>
+        <v>RU Leib-Gvardii Kazachiy</v>
       </c>
       <c r="N1" s="9" t="str">
-        <v>Yegerskiy</v>
+        <v>RU Yegerskiy</v>
       </c>
       <c r="O1" s="9" t="str">
-        <v>Pehotniy</v>
+        <v>RU Pehotniy</v>
       </c>
       <c r="P1" s="9" t="str">
-        <v>Grenaderskaya</v>
+        <v>RU Grenaderskaya</v>
       </c>
       <c r="Q1" s="9" t="str">
-        <v>Svodno-Grenaderskaya</v>
+        <v>RU Svodno-Grenaderskaya</v>
       </c>
       <c r="R1" s="9" t="str">
-        <v>Pionery</v>
+        <v>RU Pionery</v>
       </c>
       <c r="S1" s="9" t="str">
-        <v>Kirasirskiy</v>
+        <v>RU Kirasirskiy</v>
       </c>
       <c r="T1" s="9" t="str">
-        <v>Dragunskiy</v>
+        <v>RU Dragunskiy</v>
       </c>
       <c r="U1" s="9" t="str">
-        <v>Ulanskiy</v>
+        <v>RU Ulanskiy</v>
       </c>
       <c r="V1" s="9" t="str">
-        <v>Gusarskiy</v>
+        <v>RU Gusarskiy</v>
       </c>
       <c r="W1" s="9" t="str">
-        <v>Donskoy Kazachiy</v>
+        <v>RU Donskoy Kazachiy</v>
       </c>
       <c r="X1" s="9" t="str">
-        <v>Konno-Tatarskiy</v>
+        <v>RU Konno-Tatarskiy</v>
       </c>
       <c r="Y1" s="9" t="str">
-        <v>Bugskiy Kazachiy</v>
+        <v>RU Bugskiy Kazachiy</v>
       </c>
       <c r="Z1" s="9" t="str">
-        <v>Bashkirskiy Konnyy</v>
+        <v>RU Bashkirskiy Konnyy</v>
       </c>
       <c r="AA1" s="9" t="str">
-        <v>Teptyar Kazachiy</v>
+        <v>RU Teptyar Kazachiy</v>
       </c>
       <c r="AB1" s="9" t="str">
-        <v>Batareynaya Artilleriyskaya</v>
+        <v>RU Batareynaya Artilleriyskaya</v>
       </c>
       <c r="AC1" s="9" t="str">
-        <v>Legkaya Artilleriyskaya</v>
+        <v>RU Legkaya Artilleriyskaya</v>
       </c>
       <c r="AD1" s="9" t="str">
-        <v>Konno-Artilleriyskaya</v>
+        <v>RU Konno-Artilleriyskaya</v>
       </c>
       <c r="AE1" s="9" t="str">
-        <v>Donskoy Artilleriyskaya</v>
+        <v>RU Donskoy Artilleriyskaya</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -1395,6 +1395,9 @@
       <c r="AC2" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="AD2" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
@@ -1406,6 +1409,12 @@
       <c r="C3" t="str">
         <v>Enthusiastic</v>
       </c>
+      <c r="N3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="P3" s="9" t="s">
         <v>18</v>
       </c>
@@ -1416,6 +1425,9 @@
         <v>18</v>
       </c>
       <c r="AC3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="9" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1429,6 +1441,12 @@
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="N4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="Q4" s="9" t="s">
         <v>18</v>
       </c>
@@ -1439,6 +1457,9 @@
         <v>18</v>
       </c>
       <c r="AC4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD4" s="9" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1452,6 +1473,33 @@
       <c r="C5" t="str">
         <v>Rapid Deployment</v>
       </c>
+      <c r="W5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
@@ -1472,6 +1520,27 @@
       <c r="V6" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="W6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC6" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="AD6" s="9" t="s">
         <v>18</v>
       </c>
@@ -1489,6 +1558,27 @@
       <c r="S7" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="W7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC7" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="AD7" s="9" t="s">
         <v>18</v>
       </c>
@@ -1518,6 +1608,15 @@
       <c r="AA8" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="AB8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD8" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="AE8" s="9" t="s">
         <v>18</v>
       </c>
@@ -1532,6 +1631,9 @@
       <c r="C9" t="str">
         <v>Reinforcements</v>
       </c>
+      <c r="R9" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="AB9" s="9" t="s">
         <v>18</v>
       </c>
@@ -1558,6 +1660,9 @@
       <c r="E10" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="R10" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="AB10" s="9" t="s">
         <v>18</v>
       </c>
@@ -1600,6 +1705,9 @@
         <v>18</v>
       </c>
       <c r="M11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB11" s="9" t="s">
         <v>18</v>
       </c>
       <c r="AC11" s="9" t="s">

--- a/assets/ESR Formations-Russia.xlsx
+++ b/assets/ESR Formations-Russia.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9EFA18F7C2E81EA4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="8_{E90DCEA3-0D93-4AD5-83F7-85788FB57FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12A74593-D65D-4D6F-9326-2F422DA0DE98}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="8_{E90DCEA3-0D93-4AD5-83F7-85788FB57FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C24923F6-2557-4A92-A8FA-30EB1E2B6A4F}"/>
   <bookViews>
-    <workbookView xWindow="-27840" yWindow="705" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
     <sheet name="ExpandedFormations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$2)</definedName>
-    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$2)</definedName>
+    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$3)</definedName>
+    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$3)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="75">
   <si>
     <t>Formation</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t>RU Donskoy Artilleriyskaya</t>
+  </si>
+  <si>
+    <t>RU Mixed</t>
+  </si>
+  <si>
+    <t>Mixed</t>
   </si>
 </sst>
 </file>
@@ -435,13 +441,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,6 +464,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -810,34 +820,34 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11"/>
+      <c r="C2" s="12"/>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="3">
         <v>4</v>
       </c>
-      <c r="F2" s="11"/>
+      <c r="F2" s="12"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="3">
         <v>8</v>
       </c>
-      <c r="F3" s="11"/>
+      <c r="F3" s="12"/>
       <c r="I3" s="8" t="s">
         <v>45</v>
       </c>
@@ -894,13 +904,13 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -909,7 +919,7 @@
       <c r="E6" s="5">
         <v>8</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="13"/>
       <c r="I6" s="8" t="s">
         <v>48</v>
       </c>
@@ -918,16 +928,16 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="13"/>
       <c r="I7" s="8" t="s">
         <v>49</v>
       </c>
@@ -984,22 +994,22 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <v>6</v>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="12"/>
       <c r="I10" s="8" t="s">
         <v>52</v>
       </c>
@@ -1008,14 +1018,14 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
       <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="12"/>
       <c r="I11" s="8" t="s">
         <v>53</v>
       </c>
@@ -1024,20 +1034,20 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="10"/>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="13" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="8" t="s">
@@ -1048,16 +1058,16 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
       <c r="D13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="5">
         <v>2</v>
       </c>
-      <c r="F13" s="12"/>
+      <c r="F13" s="13"/>
       <c r="I13" s="8" t="s">
         <v>55</v>
       </c>
@@ -1066,16 +1076,16 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
       <c r="D14" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="5">
         <v>2</v>
       </c>
-      <c r="F14" s="12"/>
+      <c r="F14" s="13"/>
       <c r="I14" s="8" t="s">
         <v>56</v>
       </c>
@@ -1084,14 +1094,14 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5">
         <v>2</v>
       </c>
-      <c r="F15" s="12"/>
+      <c r="F15" s="13"/>
       <c r="I15" s="8" t="s">
         <v>57</v>
       </c>
@@ -1242,23 +1252,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="F10:F11"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1266,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A52F401-E5BC-41DA-8596-65382229DEB1}">
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="24.85546875" customWidth="1"/>
@@ -1369,53 +1379,113 @@
         <v>RU Donskoy Artilleriyskaya</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C11">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
+    <row r="2" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE2" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:C12">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
         <v>RU Pehotnaya Diviziya</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Infantry</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>RU Grenaderskaya Diviziya</v>
       </c>
       <c r="B3" t="str">
         <v>Infantry</v>
       </c>
       <c r="C3" t="str">
-        <v>Enthusiastic</v>
+        <v/>
       </c>
       <c r="N3" s="9" t="s">
         <v>18</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="9" t="s">
         <v>18</v>
       </c>
       <c r="R3" s="9" t="s">
@@ -1433,13 +1503,13 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>RU Svodno-Grenaderskaya Divizya</v>
+        <v>RU Grenaderskaya Diviziya</v>
       </c>
       <c r="B4" t="str">
         <v>Infantry</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>Enthusiastic</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>18</v>
@@ -1447,7 +1517,7 @@
       <c r="O4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="P4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="R4" s="9" t="s">
@@ -1465,27 +1535,24 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>RU Legkaya Kavaleriya</v>
+        <v>RU Svodno-Grenaderskaya Divizya</v>
       </c>
       <c r="B5" t="str">
-        <v>Cavalry</v>
+        <v>Infantry</v>
       </c>
       <c r="C5" t="str">
-        <v>Rapid Deployment</v>
-      </c>
-      <c r="W5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="X5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA5" s="9" t="s">
+        <v/>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="9" t="s">
         <v>18</v>
       </c>
       <c r="AB5" s="9" t="s">
@@ -1495,15 +1562,12 @@
         <v>18</v>
       </c>
       <c r="AD5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>RU Kavaleriyskaya Brigada</v>
+        <v>RU Legkaya Kavaleriya</v>
       </c>
       <c r="B6" t="str">
         <v>Cavalry</v>
@@ -1511,15 +1575,6 @@
       <c r="C6" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="T6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="U6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="V6" s="9" t="s">
-        <v>18</v>
-      </c>
       <c r="W6" s="9" t="s">
         <v>18</v>
       </c>
@@ -1542,12 +1597,15 @@
         <v>18</v>
       </c>
       <c r="AD6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE6" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>RU Kirasirskaya Brigada</v>
+        <v>RU Kavaleriyskaya Brigada</v>
       </c>
       <c r="B7" t="str">
         <v>Cavalry</v>
@@ -1555,7 +1613,13 @@
       <c r="C7" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="T7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="9" t="s">
         <v>18</v>
       </c>
       <c r="W7" s="9" t="s">
@@ -1585,13 +1649,16 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <v>RU Donskaya Kazachya Brigada</v>
+        <v>RU Kirasirskaya Brigada</v>
       </c>
       <c r="B8" t="str">
         <v>Cavalry</v>
       </c>
       <c r="C8" t="str">
-        <v>Brittle</v>
+        <v>Rapid Deployment</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>18</v>
@@ -1615,23 +1682,32 @@
         <v>18</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE8" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <v>RU Rezervnaya Artilleriya</v>
+        <v>RU Donskaya Kazachya Brigada</v>
       </c>
       <c r="B9" t="str">
-        <v>Artillery</v>
+        <v>Cavalry</v>
       </c>
       <c r="C9" t="str">
-        <v>Reinforcements</v>
-      </c>
-      <c r="R9" s="9" t="s">
+        <v>Brittle</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA9" s="9" t="s">
         <v>18</v>
       </c>
       <c r="AB9" s="9" t="s">
@@ -1641,24 +1717,21 @@
         <v>18</v>
       </c>
       <c r="AD9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE9" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
-        <v>RU Leib-Gvardii Diviziya</v>
+        <v>RU Rezervnaya Artilleriya</v>
       </c>
       <c r="B10" t="str">
-        <v>Infantry</v>
+        <v>Artillery</v>
       </c>
       <c r="C10" t="str">
-        <v>Enthusiastic</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>18</v>
+        <v>Reinforcements</v>
       </c>
       <c r="R10" s="9" t="s">
         <v>18</v>
@@ -1675,45 +1748,74 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
+        <v>RU Leib-Gvardii Diviziya</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Infantry</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Enthusiastic</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD11" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
         <v>RU Leib-Gvardii Kavaleriya Brigada</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B12" t="str">
         <v>Cavalry</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C12" t="str">
         <v xml:space="preserve">	Rapid Deployment</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD11" s="9" t="s">
+      <c r="F12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD12" s="9" t="s">
         <v>18</v>
       </c>
     </row>
